--- a/docs/validation/V14_Pareto_Accumulation.xlsx
+++ b/docs/validation/V14_Pareto_Accumulation.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1291,988 +1291,1119 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="46" customHeight="1">
-      <c r="B65" s="17" t="inlineStr">
+    <row r="65" ht="16" customHeight="1">
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>4.2b Part 1b — repeat it under each slicer choice</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="43" customHeight="1">
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>The criterion says under every slicer combination, and the chart cannot show that: 7.5 plots the top 100 items only. This version applies one filter the way a slicer does. Run it once for each year that has data, changing 2024 each time, then once for each item type, replacing the last filter line with DimItem[ItemType] = "Wine", then "Liquor", "Beer" and "Kegs".</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>EVALUATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>CALCULATETABLE (</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOPN (</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        1,</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ADDCOLUMNS (</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            VALUES ( DimItem[ItemDescription] ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            "Rank",       [Item Rank by Volume],</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            "Cumulative", [Cumulative Cases %]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        [Rank], DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DimDate[Year] = 2024    -- change this one line for each run</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="29.5" customHeight="1">
+      <c r="A80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>For every run, write down the filter and the Cumulative value. Each must be exactly 1. Items that moved nothing under the filter have no rank and are skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="46" customHeight="1">
+      <c r="B81" s="17" t="inlineStr">
         <is>
           <t>When you have written the result down.  Close the query tab with the × on its tab. Queries left open in DAX query view are kept with the file, and the model file should hold nothing but the model. Then close Power BI Desktop without saving, unless you changed something on purpose.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="B66" s="13" t="inlineStr">
+    <row r="82" ht="20" customHeight="1">
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>4.3 Open the R3 report file</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="16" t="n">
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>Open File Explorer and go to X:\retail-sector-health\pbip.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="16" t="n">
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>Double-click the R3 file — the R3 file. Power BI Desktop opens it and shows the first report page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="16" t="n">
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>Double-click the R3 file — R3_Assortment_Supplier.pbip. Power BI Desktop opens it and shows the first report page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B69" s="14" t="inlineStr">
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>The page tabs run along the bottom of the window: Page 1, Page 2 and so on. Select a tab to move to that page.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="16" t="n">
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B70" s="14" t="inlineStr">
+      <c r="B86" s="14" t="inlineStr">
         <is>
           <t>To inspect one visual, click it once. A thin frame appears around it. Then look at the Visualizations pane on the right:</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="29" customHeight="1">
-      <c r="B71" s="19" t="inlineStr">
+    <row r="87" ht="29" customHeight="1">
+      <c r="B87" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
         <is>
           <t>The Build visual icon (the first icon, a small chart) shows the wells — X-axis, Y-axis, Column y-axis, Line y-axis, Legend, Values — and exactly which field or measure sits in each.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="29" customHeight="1">
-      <c r="B72" s="19" t="inlineStr">
+    <row r="88" ht="29" customHeight="1">
+      <c r="B88" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>The Format visual icon (the paintbrush) shows the formatting, including the Y-axis and Secondary y-axis sections.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="29" customHeight="1">
-      <c r="B73" s="19" t="inlineStr">
+    <row r="89" ht="29" customHeight="1">
+      <c r="B89" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C73" s="14" t="inlineStr">
+      <c r="C89" s="14" t="inlineStr">
         <is>
           <t>The Filters pane, to the left of the Visualizations pane, shows the filters on this visual, on this page and on all pages. Select the arrow at its edge to open it if it is collapsed.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="B74" s="13" t="inlineStr">
+    <row r="90" ht="20" customHeight="1">
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>4.4 Part 2 — check the chart under each slicer choice (once R3 Page 1 exists)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="16" t="n">
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>Go to Page 1. Find visual 7.5, the Pareto chart. The line is on the secondary axis on the right, running 0 to 100%.</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="16" t="n">
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>Hover over the right-most point of the line. The tooltip shows its value. Note it.</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="16" t="n">
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>Pick each value in the page’s slicers in turn and repeat: after each change, hover over the right-most point.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="29" customHeight="1">
-      <c r="A78" s="16" t="n">
+    <row r="94" ht="29.5" customHeight="1">
+      <c r="A94" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>Note that the chart shows the top 100 items only, so its last point may be below 100%. The query in Part 1, which ranks all items, is the test of the criterion; Part 2 checks that the line never goes above 100% and behaves under every slicer choice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="8" customHeight="1"/>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>Note that the chart shows the top 100 items only, so its last point may be below 100%. The queries in Parts 1 and 1b, which rank all items, are the test of the criterion; Part 2 checks that the line never goes above 100% and behaves under every slicer choice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>5. DECIDE: PASS OR FAIL</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="B81" s="14" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>Decide against the pass criterion only — it is repeated in At a Glance. Find the row below that matches what you saw.</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="B82" s="6" t="inlineStr">
+    <row r="98" ht="20" customHeight="1">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>If you see</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>It means</t>
         </is>
       </c>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="70" customHeight="1">
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>Cumulative is exactly 1 in Part 1, and in Part 2 no selection breaks the line or pushes it above 100%</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="F98" s="8" t="n"/>
+    </row>
+    <row r="99" ht="83.5" customHeight="1">
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Cumulative is exactly 1 in Part 1 and in every Part 1b run, and in Part 2 no selection breaks the line or pushes it above 100%</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>Ranking and total agree</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n"/>
-    </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>Cumulative is below 1 in Part 1</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="F99" s="8" t="n"/>
+    </row>
+    <row r="100" ht="43" customHeight="1">
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>Cumulative is below 1 in Part 1 or in any Part 1b run</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
         <is>
           <t>Ranking and total use different sets of items</t>
         </is>
       </c>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n"/>
-    </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="B85" s="10" t="inlineStr">
+      <c r="F100" s="8" t="n"/>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="B101" s="10" t="inlineStr">
         <is>
           <t>Any point above 100% in Part 2</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>The total is smaller than the running sum — a context error</t>
         </is>
       </c>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="10" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F85" s="8" t="n"/>
-    </row>
-    <row r="86" ht="8" customHeight="1"/>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="F101" s="8" t="n"/>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>6. RECORD THE RESULT</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="B88" s="13" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="B104" s="13" t="inlineStr">
         <is>
           <t>6.1 In document 22</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="16" t="n">
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B105" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="16" t="n">
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B90" s="14" t="inlineStr">
+      <c r="B106" s="14" t="inlineStr">
         <is>
           <t>Select the Run Summary tab. Find the row for this run.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="29" customHeight="1">
-      <c r="B91" s="19" t="inlineStr">
+    <row r="107" ht="29" customHeight="1">
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C91" s="14" t="inlineStr">
+      <c r="C107" s="14" t="inlineStr">
         <is>
           <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="29" customHeight="1">
-      <c r="B92" s="19" t="inlineStr">
+    <row r="108" ht="29" customHeight="1">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C108" s="14" t="inlineStr">
         <is>
           <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="29" customHeight="1">
-      <c r="B93" s="19" t="inlineStr">
+    <row r="109" ht="29" customHeight="1">
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C93" s="14" t="inlineStr">
+      <c r="C109" s="14" t="inlineStr">
         <is>
           <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="B94" s="19" t="inlineStr">
+    <row r="110" ht="16" customHeight="1">
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C94" s="14" t="inlineStr">
+      <c r="C110" s="14" t="inlineStr">
         <is>
           <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="B95" s="18" t="inlineStr">
+    <row r="111" ht="15" customHeight="1">
+      <c r="B111" s="18" t="inlineStr">
         <is>
           <t>git -C X:\retail-sector-health log -1 --format=%h</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="6" customHeight="1"/>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="16" t="n">
+    <row r="112" ht="6" customHeight="1"/>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B97" s="14" t="inlineStr">
+      <c r="B113" s="14" t="inlineStr">
         <is>
           <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 14.</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="16" t="n">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B98" s="14" t="inlineStr">
+      <c r="B114" s="14" t="inlineStr">
         <is>
           <t>Fill in four cells on that row:</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="B99" s="19" t="inlineStr">
+    <row r="115" ht="16" customHeight="1">
+      <c r="B115" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C99" s="14" t="inlineStr">
+      <c r="C115" s="14" t="inlineStr">
         <is>
           <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="B100" s="19" t="inlineStr">
+    <row r="116" ht="16" customHeight="1">
+      <c r="B116" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C100" s="14" t="inlineStr">
+      <c r="C116" s="14" t="inlineStr">
         <is>
           <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="B101" s="19" t="inlineStr">
+    <row r="117" ht="16" customHeight="1">
+      <c r="B117" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C101" s="14" t="inlineStr">
+      <c r="C117" s="14" t="inlineStr">
         <is>
           <t>Checked by: your name or initials.</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="B102" s="19" t="inlineStr">
+    <row r="118" ht="16" customHeight="1">
+      <c r="B118" s="19" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C102" s="14" t="inlineStr">
+      <c r="C118" s="14" t="inlineStr">
         <is>
           <t>Date checked: today’s date.</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="16" t="n">
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B103" s="14" t="inlineStr">
+      <c r="B119" s="14" t="inlineStr">
         <is>
           <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="B104" s="6" t="inlineStr">
+    <row r="120" ht="20" customHeight="1">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>Write this in Observed value / evidence</t>
         </is>
       </c>
-      <c r="D104" s="7" t="n"/>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="8" t="n"/>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="B105" s="10" t="inlineStr">
+      <c r="D120" s="7" t="n"/>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="8" t="n"/>
+    </row>
+    <row r="121" ht="29.5" customHeight="1">
+      <c r="B121" s="10" t="inlineStr">
         <is>
           <t>Example of a pass</t>
         </is>
       </c>
-      <c r="C105" s="10" t="inlineStr">
-        <is>
-          <t>Model: lowest rank 2,640, Cumulative 1.000 · R3 P1 7.5: no selection exceeds 100%</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="n"/>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="8" t="n"/>
-    </row>
-    <row r="106" ht="28" customHeight="1">
-      <c r="B106" s="12" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>Model: lowest rank 2,640, Cumulative 1.000 · Part 1b: every year and all four item types 1.000 · R3 P1 7.5: no selection exceeds 100%</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="8" t="n"/>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>Example of another result</t>
         </is>
       </c>
-      <c r="C106" s="12" t="inlineStr">
+      <c r="C122" s="12" t="inlineStr">
         <is>
           <t>Cumulative 0.964 at the lowest rank — ranking and total contexts differ</t>
         </is>
       </c>
-      <c r="D106" s="7" t="n"/>
-      <c r="E106" s="7" t="n"/>
-      <c r="F106" s="8" t="n"/>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="B107" s="20" t="inlineStr">
+      <c r="D122" s="7" t="n"/>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="8" t="n"/>
+    </row>
+    <row r="123" ht="16" customHeight="1">
+      <c r="B123" s="20" t="inlineStr">
         <is>
           <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="B108" s="13" t="inlineStr">
+    <row r="124" ht="20" customHeight="1">
+      <c r="B124" s="13" t="inlineStr">
         <is>
           <t>6.2 In document 26</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="16" t="n">
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B109" s="14" t="inlineStr">
+      <c r="B125" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="29" customHeight="1">
-      <c r="A110" s="16" t="n">
+    <row r="126" ht="29" customHeight="1">
+      <c r="A126" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B110" s="14" t="inlineStr">
+      <c r="B126" s="14" t="inlineStr">
         <is>
           <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="B111" s="6" t="inlineStr">
+    <row r="127" ht="20" customHeight="1">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Ref in doc 26</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>When it applies</t>
         </is>
       </c>
-      <c r="D111" s="7" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8" t="n"/>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="B112" s="10" t="inlineStr">
+      <c r="D127" s="7" t="n"/>
+      <c r="E127" s="7" t="n"/>
+      <c r="F127" s="8" t="n"/>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="B128" s="10" t="inlineStr">
         <is>
           <t>G4.08</t>
         </is>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>When folder 08 Assortment closes</t>
         </is>
       </c>
-      <c r="D112" s="7" t="n"/>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="8" t="n"/>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="B113" s="12" t="inlineStr">
+      <c r="D128" s="7" t="n"/>
+      <c r="E128" s="7" t="n"/>
+      <c r="F128" s="8" t="n"/>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>G5.12</t>
         </is>
       </c>
-      <c r="C113" s="12" t="inlineStr">
+      <c r="C129" s="12" t="inlineStr">
         <is>
           <t>The model pass</t>
         </is>
       </c>
-      <c r="D113" s="7" t="n"/>
-      <c r="E113" s="7" t="n"/>
-      <c r="F113" s="8" t="n"/>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="B114" s="10" t="inlineStr">
+      <c r="D129" s="7" t="n"/>
+      <c r="E129" s="7" t="n"/>
+      <c r="F129" s="8" t="n"/>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="B130" s="10" t="inlineStr">
         <is>
           <t>G7.10</t>
         </is>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>R3 Page 1 finished</t>
         </is>
       </c>
-      <c r="D114" s="7" t="n"/>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="8" t="n"/>
-    </row>
-    <row r="115" ht="8" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>7. IF IT FAILS</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="B117" s="13" t="inlineStr">
-        <is>
-          <t>7.1 What usually causes it</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>What you see</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>Likely cause</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>What to do</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="n"/>
-    </row>
-    <row r="119" ht="28" customHeight="1">
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t>Below 1</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
-        <is>
-          <t>The two ALLSELECTED calls in Cumulative Cases % use different columns</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="10" t="inlineStr">
-        <is>
-          <t>Check the measure in document 02 §8.11; both must rank over DimItem[ItemDescription]</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="B120" s="12" t="inlineStr">
-        <is>
-          <t>Above 100% on the chart</t>
-        </is>
-      </c>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>A visual-level filter applies to the rank but not the total</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="n"/>
-      <c r="E120" s="12" t="inlineStr">
-        <is>
-          <t>Remove the filter or apply it to both</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="n"/>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="B121" s="13" t="inlineStr">
-        <is>
-          <t>7.2 Record the failure</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="29" customHeight="1">
-      <c r="A122" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B122" s="14" t="inlineStr">
-        <is>
-          <t>On the Check Results tab of document 22, set Result to Fail for check 14. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B123" s="14" t="inlineStr">
-        <is>
-          <t>Select the Failure Log tab and fill the first empty row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="B124" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C124" s="14" t="inlineStr">
-        <is>
-          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="B125" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C125" s="14" t="inlineStr">
-        <is>
-          <t>Run ID and Check #: this run and check number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="B126" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C126" s="14" t="inlineStr">
-        <is>
-          <t>What was observed: the same numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="B127" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C127" s="14" t="inlineStr">
-        <is>
-          <t>Root cause: what you found, or ‘not yet known’.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B128" s="14" t="inlineStr">
-        <is>
-          <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="29" customHeight="1">
-      <c r="A129" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B129" s="14" t="inlineStr">
-        <is>
-          <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B130" s="14" t="inlineStr">
-        <is>
-          <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
-        </is>
-      </c>
+      <c r="D130" s="7" t="n"/>
+      <c r="E130" s="7" t="n"/>
+      <c r="F130" s="8" t="n"/>
     </row>
     <row r="131" ht="8" customHeight="1"/>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
+          <t>7. IF IT FAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>7.1 What usually causes it</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>What you see</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>Likely cause</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="n"/>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="n"/>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>Below 1</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>The two ALLSELECTED calls in Cumulative Cases % use different columns</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>Check the measure in document 02 §8.11; both must rank over DimItem[ItemDescription]</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>Above 100% on the chart</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>A visual-level filter applies to the rank but not the total</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>Remove the filter or apply it to both</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="n"/>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="B137" s="13" t="inlineStr">
+        <is>
+          <t>7.2 Record the failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="29" customHeight="1">
+      <c r="A138" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B138" s="14" t="inlineStr">
+        <is>
+          <t>On the Check Results tab of document 22, set Result to Fail for check 14. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>Select the Failure Log tab and fill the first empty row:</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="B140" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="B141" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>Run ID and Check #: this run and check number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="B142" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="inlineStr">
+        <is>
+          <t>What was observed: the same numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="B143" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>Root cause: what you found, or ‘not yet known’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="29" customHeight="1">
+      <c r="A145" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
+        <is>
+          <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="8" customHeight="1"/>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="15" t="inlineStr">
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B133" s="14" t="inlineStr">
+      <c r="B149" s="14" t="inlineStr">
         <is>
           <t>At the model pass.</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="15" t="inlineStr">
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B134" s="14" t="inlineStr">
+      <c r="B150" s="14" t="inlineStr">
         <is>
           <t>After any edit to a folder 08 measure.</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="15" t="inlineStr">
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B135" s="14" t="inlineStr">
+      <c r="B151" s="14" t="inlineStr">
         <is>
           <t>After every reload of the county data.</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="8" customHeight="1"/>
-    <row r="137" ht="22" customHeight="1">
-      <c r="A137" s="5" t="inlineStr">
+    <row r="152" ht="8" customHeight="1"/>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="15" t="inlineStr">
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B138" s="14" t="inlineStr">
+      <c r="B154" s="14" t="inlineStr">
         <is>
           <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="15" t="inlineStr">
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B139" s="14" t="inlineStr">
+      <c r="B155" s="14" t="inlineStr">
         <is>
           <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="15" t="inlineStr">
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B140" s="14" t="inlineStr">
+      <c r="B156" s="14" t="inlineStr">
         <is>
           <t>Document 25 — when each check is run, and when to re-run it.</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="15" t="inlineStr">
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B141" s="14" t="inlineStr">
+      <c r="B157" s="14" t="inlineStr">
         <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="B142" s="21" t="inlineStr">
+    <row r="158" ht="18" customHeight="1">
+      <c r="B158" s="21" t="inlineStr">
         <is>
           <t>Work with DAX query view</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="8" customHeight="1"/>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+    <row r="159" ht="8" customHeight="1"/>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="29" customHeight="1">
-      <c r="B145" s="14" t="inlineStr">
+    <row r="161" ht="29" customHeight="1">
+      <c r="B161" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="43.5" customHeight="1">
-      <c r="B146" s="14" t="inlineStr">
+    <row r="162" ht="43.5" customHeight="1">
+      <c r="B162" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="141">
-    <mergeCell ref="B129:F129"/>
+  <mergeCells count="157">
+    <mergeCell ref="B106:F106"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B81:F81"/>
+    <mergeCell ref="C122:F122"/>
+    <mergeCell ref="C98:D98"/>
     <mergeCell ref="B90:F90"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="B71:F71"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="C87:F87"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="C134:D134"/>
     <mergeCell ref="B60:F60"/>
-    <mergeCell ref="A144:F144"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C107:F107"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="C116:F116"/>
+    <mergeCell ref="B53:F53"/>
     <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="E99:F99"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="C73:F73"/>
+    <mergeCell ref="C88:F88"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C120:D120"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B108:F108"/>
     <mergeCell ref="A40:F40"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="C121:F121"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C93:F93"/>
-    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="E100:F100"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="C105:F105"/>
+    <mergeCell ref="E136:F136"/>
     <mergeCell ref="B133:F133"/>
-    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B94:F94"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="B135:F135"/>
-    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C120:F120"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="B72:F72"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="B70:F70"/>
-    <mergeCell ref="C111:F111"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="C92:F92"/>
-    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B111:F111"/>
     <mergeCell ref="C30:F30"/>
-    <mergeCell ref="B107:F107"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B162:F162"/>
     <mergeCell ref="B146:F146"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="E120:F120"/>
-    <mergeCell ref="C124:F124"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B45:F45"/>
-    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="B126:F126"/>
+    <mergeCell ref="C110:F110"/>
     <mergeCell ref="B75:F75"/>
-    <mergeCell ref="A137:F137"/>
-    <mergeCell ref="B109:F109"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C91:F91"/>
-    <mergeCell ref="B141:F141"/>
     <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B150:F150"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="C102:F102"/>
-    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C100:D100"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="A116:F116"/>
-    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="B161:F161"/>
     <mergeCell ref="B145:F145"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="C108:F108"/>
+    <mergeCell ref="C141:F141"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="C128:F128"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="C113:F113"/>
+    <mergeCell ref="C143:F143"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="C100:F100"/>
-    <mergeCell ref="C112:F112"/>
-    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="C109:F109"/>
+    <mergeCell ref="B65:F65"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="B65:F65"/>
     <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C142:F142"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C114:F114"/>
+    <mergeCell ref="C129:F129"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E134:F134"/>
     <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B154:F154"/>
     <mergeCell ref="B123:F123"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="A87:F87"/>
     <mergeCell ref="B138:F138"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B91:F91"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C106:F106"/>
-    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="E98:F98"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="C140:F140"/>
     <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B117:F117"/>
-    <mergeCell ref="C101:F101"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B151:F151"/>
+    <mergeCell ref="C99:D99"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C104:F104"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B103:F103"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C117:F117"/>
+    <mergeCell ref="A148:F148"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C118:F118"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B89:F89"/>
     <mergeCell ref="A132:F132"/>
+    <mergeCell ref="B104:F104"/>
     <mergeCell ref="B51:F51"/>
+    <mergeCell ref="C115:F115"/>
+    <mergeCell ref="C130:F130"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="B79:F79"/>
     <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C136:D136"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B35:F35"/>

--- a/docs/validation/V14_Pareto_Accumulation.xlsx
+++ b/docs/validation/V14_Pareto_Accumulation.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -677,10 +677,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Check 14 of 17 · Model pass · Recorded in document 22 · Gates G4, G5, G7</t>
+          <t>Check 14 of 17 · Model pass · Recorded in document 22 · Gates G4, G5, G7, G8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>G4, G5 and G7</t>
+          <t>G4, G5, G7 and G8</t>
         </is>
       </c>
       <c r="D15" s="7" t="n"/>
@@ -1942,114 +1942,117 @@
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="8" t="n"/>
     </row>
-    <row r="131" ht="8" customHeight="1"/>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
+    <row r="131" ht="16" customHeight="1">
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>G8.05</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>R3 report pass</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="8" t="n"/>
+    </row>
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>7. IF IT FAILS</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="B133" s="13" t="inlineStr">
+    <row r="134" ht="20" customHeight="1">
+      <c r="B134" s="13" t="inlineStr">
         <is>
           <t>7.1 What usually causes it</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="B134" s="6" t="inlineStr">
+    <row r="135" ht="20" customHeight="1">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>What you see</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
         <is>
           <t>Likely cause</t>
         </is>
       </c>
-      <c r="D134" s="8" t="n"/>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="6" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
-      <c r="F134" s="8" t="n"/>
-    </row>
-    <row r="135" ht="28" customHeight="1">
-      <c r="B135" s="10" t="inlineStr">
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>Below 1</t>
         </is>
       </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="C136" s="10" t="inlineStr">
         <is>
           <t>The two ALLSELECTED calls in Cumulative Cases % use different columns</t>
         </is>
       </c>
-      <c r="D135" s="8" t="n"/>
-      <c r="E135" s="10" t="inlineStr">
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="10" t="inlineStr">
         <is>
           <t>Check the measure in document 02 §8.11; both must rank over DimItem[ItemDescription]</t>
         </is>
       </c>
-      <c r="F135" s="8" t="n"/>
-    </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="B136" s="12" t="inlineStr">
+      <c r="F136" s="8" t="n"/>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="B137" s="12" t="inlineStr">
         <is>
           <t>Above 100% on the chart</t>
         </is>
       </c>
-      <c r="C136" s="12" t="inlineStr">
+      <c r="C137" s="12" t="inlineStr">
         <is>
           <t>A visual-level filter applies to the rank but not the total</t>
         </is>
       </c>
-      <c r="D136" s="8" t="n"/>
-      <c r="E136" s="12" t="inlineStr">
+      <c r="D137" s="8" t="n"/>
+      <c r="E137" s="12" t="inlineStr">
         <is>
           <t>Remove the filter or apply it to both</t>
         </is>
       </c>
-      <c r="F136" s="8" t="n"/>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="B137" s="13" t="inlineStr">
+      <c r="F137" s="8" t="n"/>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="B138" s="13" t="inlineStr">
         <is>
           <t>7.2 Record the failure</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="29" customHeight="1">
-      <c r="A138" s="16" t="n">
+    <row r="139" ht="29" customHeight="1">
+      <c r="A139" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B138" s="14" t="inlineStr">
+      <c r="B139" s="14" t="inlineStr">
         <is>
           <t>On the Check Results tab of document 22, set Result to Fail for check 14. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="16" t="n">
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B139" s="14" t="inlineStr">
+      <c r="B140" s="14" t="inlineStr">
         <is>
           <t>Select the Failure Log tab and fill the first empty row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="B140" s="19" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C140" s="14" t="inlineStr">
-        <is>
-          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2064,7 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>Run ID and Check #: this run and check number.</t>
+          <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2076,7 @@
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>What was observed: the same numbers.</t>
+          <t>Run ID and Check #: this run and check number.</t>
         </is>
       </c>
     </row>
@@ -2085,57 +2088,57 @@
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
+          <t>What was observed: the same numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="B144" s="19" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr">
+        <is>
           <t>Root cause: what you found, or ‘not yet known’.</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="16" t="n">
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B144" s="14" t="inlineStr">
+      <c r="B145" s="14" t="inlineStr">
         <is>
           <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="29" customHeight="1">
-      <c r="A145" s="16" t="n">
+    <row r="146" ht="29" customHeight="1">
+      <c r="A146" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B145" s="14" t="inlineStr">
+      <c r="B146" s="14" t="inlineStr">
         <is>
           <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="16" t="n">
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B146" s="14" t="inlineStr">
+      <c r="B147" s="14" t="inlineStr">
         <is>
           <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="8" customHeight="1"/>
-    <row r="148" ht="22" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
+    <row r="148" ht="8" customHeight="1"/>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B149" s="14" t="inlineStr">
-        <is>
-          <t>At the model pass.</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2150,7 @@
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>After any edit to a folder 08 measure.</t>
+          <t>At the model pass.</t>
         </is>
       </c>
     </row>
@@ -2159,27 +2162,27 @@
       </c>
       <c r="B151" s="14" t="inlineStr">
         <is>
+          <t>After any edit to a folder 08 measure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
           <t>After every reload of the county data.</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="8" customHeight="1"/>
-    <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
+    <row r="153" ht="8" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="15" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B154" s="14" t="inlineStr">
-        <is>
-          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2194,7 @@
       </c>
       <c r="B155" s="14" t="inlineStr">
         <is>
-          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
+          <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2206,7 @@
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>Document 25 — when each check is run, and when to re-run it.</t>
+          <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
@@ -2215,65 +2218,79 @@
       </c>
       <c r="B157" s="14" t="inlineStr">
         <is>
+          <t>Document 25 — when each check is run, and when to re-run it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="15" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="inlineStr">
+        <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="B158" s="21" t="inlineStr">
+    <row r="159" ht="18" customHeight="1">
+      <c r="B159" s="21" t="inlineStr">
         <is>
           <t>Work with DAX query view</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="8" customHeight="1"/>
-    <row r="160" ht="22" customHeight="1">
-      <c r="A160" s="5" t="inlineStr">
+    <row r="160" ht="8" customHeight="1"/>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="29" customHeight="1">
-      <c r="B161" s="14" t="inlineStr">
+    <row r="162" ht="29" customHeight="1">
+      <c r="B162" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="43.5" customHeight="1">
-      <c r="B162" s="14" t="inlineStr">
+    <row r="163" ht="43.5" customHeight="1">
+      <c r="B163" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="157">
+  <mergeCells count="158">
     <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B81:F81"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B81:F81"/>
     <mergeCell ref="C122:F122"/>
+    <mergeCell ref="C144:F144"/>
     <mergeCell ref="C98:D98"/>
     <mergeCell ref="B90:F90"/>
+    <mergeCell ref="A133:F133"/>
     <mergeCell ref="B71:F71"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A160:F160"/>
     <mergeCell ref="C87:F87"/>
     <mergeCell ref="B42:F42"/>
-    <mergeCell ref="C134:D134"/>
     <mergeCell ref="B60:F60"/>
+    <mergeCell ref="E137:F137"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C107:F107"/>
+    <mergeCell ref="C89:F89"/>
     <mergeCell ref="B157:F157"/>
-    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="B53:F53"/>
     <mergeCell ref="C116:F116"/>
-    <mergeCell ref="B53:F53"/>
     <mergeCell ref="B44:F44"/>
+    <mergeCell ref="A161:F161"/>
     <mergeCell ref="E99:F99"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="C88:F88"/>
@@ -2281,99 +2298,100 @@
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="C121:F121"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="E101:F101"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="B84:F84"/>
     <mergeCell ref="B92:F92"/>
     <mergeCell ref="B158:F158"/>
     <mergeCell ref="E100:F100"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="E136:F136"/>
-    <mergeCell ref="B133:F133"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B94:F94"/>
+    <mergeCell ref="C120:F120"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C120:F120"/>
-    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="A149:F149"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="C28:F28"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B105:F105"/>
     <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B111:F111"/>
     <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C137:D137"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="C14:F14"/>
     <mergeCell ref="B57:F57"/>
-    <mergeCell ref="C14:F14"/>
     <mergeCell ref="B82:F82"/>
     <mergeCell ref="B162:F162"/>
     <mergeCell ref="B146:F146"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B68:F68"/>
     <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B68:F68"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="A153:F153"/>
     <mergeCell ref="B126:F126"/>
+    <mergeCell ref="B75:F75"/>
     <mergeCell ref="C110:F110"/>
-    <mergeCell ref="B75:F75"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="E135:F135"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="C100:D100"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B161:F161"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="C108:F108"/>
     <mergeCell ref="C141:F141"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="C128:F128"/>
+    <mergeCell ref="B147:F147"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C143:F143"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="B137:F137"/>
     <mergeCell ref="C109:F109"/>
+    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C127:F127"/>
     <mergeCell ref="C142:F142"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C129:F129"/>
     <mergeCell ref="B139:F139"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="B114:F114"/>
-    <mergeCell ref="C21:F21"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B163:F163"/>
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="C101:D101"/>
     <mergeCell ref="B138:F138"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="B113:F113"/>
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="B156:F156"/>
     <mergeCell ref="E98:F98"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B140:F140"/>
     <mergeCell ref="B155:F155"/>
     <mergeCell ref="B93:F93"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="C140:F140"/>
+    <mergeCell ref="C131:F131"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B151:F151"/>
@@ -2387,20 +2405,18 @@
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C117:F117"/>
     <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C117:F117"/>
-    <mergeCell ref="A148:F148"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C118:F118"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="A132:F132"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="B51:F51"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="C130:F130"/>
     <mergeCell ref="C115:F115"/>
-    <mergeCell ref="C130:F130"/>
-    <mergeCell ref="A6:F6"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C136:D136"/>
